--- a/product_selector_out/STM32F7 series - diff.xlsx
+++ b/product_selector_out/STM32F7 series - diff.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Diff" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Diff'!$A$18:$E$214</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Diff'!$A$18:$E$215</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -33,7 +33,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -65,6 +65,11 @@
         <fgColor rgb="00F4CCCC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -81,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -91,6 +96,7 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -456,7 +462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E214"/>
+  <dimension ref="A1:E215"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -559,7 +565,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -629,7 +635,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5496</v>
+        <v>5495</v>
       </c>
     </row>
     <row r="18">
@@ -4535,18 +4541,22 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C183" t="inlineStr"/>
+          <t>D/A Converters (12-bit) typ</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E183" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E183" s="7" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
         </is>
       </c>
     </row>
@@ -4558,13 +4568,13 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C184" t="inlineStr"/>
       <c r="D184" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E184" s="3" t="inlineStr">
@@ -4576,18 +4586,18 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>STM32F746ZE</t>
+          <t>STM32F723VC</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C185" t="inlineStr"/>
       <c r="D185" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E185" s="3" t="inlineStr">
@@ -4604,13 +4614,13 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C186" t="inlineStr"/>
       <c r="D186" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E186" s="3" t="inlineStr">
@@ -4622,18 +4632,18 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>STM32F746IG</t>
+          <t>STM32F746ZE</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C187" t="inlineStr"/>
       <c r="D187" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E187" s="3" t="inlineStr">
@@ -4650,13 +4660,13 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C188" t="inlineStr"/>
       <c r="D188" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E188" s="3" t="inlineStr">
@@ -4668,18 +4678,18 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>STM32F756NG</t>
+          <t>STM32F746IG</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C189" t="inlineStr"/>
       <c r="D189" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E189" s="3" t="inlineStr">
@@ -4696,13 +4706,13 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C190" t="inlineStr"/>
       <c r="D190" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E190" s="3" t="inlineStr">
@@ -4714,18 +4724,18 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>STM32F756ZG</t>
+          <t>STM32F756NG</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C191" t="inlineStr"/>
       <c r="D191" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E191" s="3" t="inlineStr">
@@ -4742,13 +4752,13 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C192" t="inlineStr"/>
       <c r="D192" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E192" s="3" t="inlineStr">
@@ -4760,18 +4770,18 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>STM32F746VE</t>
+          <t>STM32F756ZG</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C193" t="inlineStr"/>
       <c r="D193" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E193" s="3" t="inlineStr">
@@ -4788,13 +4798,13 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C194" t="inlineStr"/>
       <c r="D194" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E194" s="3" t="inlineStr">
@@ -4806,18 +4816,18 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>STM32F746ZG</t>
+          <t>STM32F746VE</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C195" t="inlineStr"/>
       <c r="D195" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E195" s="3" t="inlineStr">
@@ -4834,13 +4844,13 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C196" t="inlineStr"/>
       <c r="D196" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E196" s="3" t="inlineStr">
@@ -4852,18 +4862,18 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>STM32F746VG</t>
+          <t>STM32F746ZG</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C197" t="inlineStr"/>
       <c r="D197" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E197" s="3" t="inlineStr">
@@ -4880,13 +4890,13 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C198" t="inlineStr"/>
       <c r="D198" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E198" s="3" t="inlineStr">
@@ -4898,18 +4908,18 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>STM32F746IE</t>
+          <t>STM32F746VG</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C199" t="inlineStr"/>
       <c r="D199" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E199" s="3" t="inlineStr">
@@ -4926,13 +4936,13 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C200" t="inlineStr"/>
       <c r="D200" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E200" s="3" t="inlineStr">
@@ -4944,18 +4954,18 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>STM32F756IG</t>
+          <t>STM32F746IE</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C201" t="inlineStr"/>
       <c r="D201" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E201" s="3" t="inlineStr">
@@ -4972,13 +4982,13 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C202" t="inlineStr"/>
       <c r="D202" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E202" s="3" t="inlineStr">
@@ -4990,18 +5000,18 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>STM32F746BG</t>
+          <t>STM32F756IG</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C203" t="inlineStr"/>
       <c r="D203" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E203" s="3" t="inlineStr">
@@ -5018,13 +5028,13 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C204" t="inlineStr"/>
       <c r="D204" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E204" s="3" t="inlineStr">
@@ -5036,18 +5046,18 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>STM32F746NG</t>
+          <t>STM32F746BG</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C205" t="inlineStr"/>
       <c r="D205" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E205" s="3" t="inlineStr">
@@ -5064,13 +5074,13 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C206" t="inlineStr"/>
       <c r="D206" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E206" s="3" t="inlineStr">
@@ -5082,18 +5092,18 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>STM32F756VG</t>
+          <t>STM32F746NG</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C207" t="inlineStr"/>
       <c r="D207" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E207" s="3" t="inlineStr">
@@ -5110,13 +5120,13 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C208" t="inlineStr"/>
       <c r="D208" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E208" s="3" t="inlineStr">
@@ -5128,18 +5138,18 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>STM32F746BE</t>
+          <t>STM32F756VG</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C209" t="inlineStr"/>
       <c r="D209" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E209" s="3" t="inlineStr">
@@ -5156,13 +5166,13 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C210" t="inlineStr"/>
       <c r="D210" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E210" s="3" t="inlineStr">
@@ -5174,18 +5184,18 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>STM32F746NE</t>
+          <t>STM32F746BE</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C211" t="inlineStr"/>
       <c r="D211" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E211" s="3" t="inlineStr">
@@ -5202,13 +5212,13 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C212" t="inlineStr"/>
       <c r="D212" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E212" s="3" t="inlineStr">
@@ -5220,18 +5230,18 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>STM32F756BG</t>
+          <t>STM32F746NE</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C213" t="inlineStr"/>
       <c r="D213" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E213" s="3" t="inlineStr">
@@ -5248,13 +5258,13 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C214" t="inlineStr"/>
       <c r="D214" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E214" s="3" t="inlineStr">
@@ -5263,8 +5273,31 @@
         </is>
       </c>
     </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>STM32F756BG</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr"/>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E215" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A18:E214"/>
+  <autoFilter ref="A18:E215"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/product_selector_out/STM32F7 series - diff.xlsx
+++ b/product_selector_out/STM32F7 series - diff.xlsx
@@ -525,7 +525,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5676</v>
+        <v>5762</v>
       </c>
     </row>
     <row r="6">
@@ -545,7 +545,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5495</v>
+        <v>5581</v>
       </c>
     </row>
     <row r="18">
